--- a/backlog (1).xlsx
+++ b/backlog (1).xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="45">
   <si>
     <t>Rzeczy do zrobienia</t>
   </si>
@@ -155,7 +155,16 @@
     <t>Kuba, Kajetan, Dawid</t>
   </si>
   <si>
-    <t>❌polowa</t>
+    <t xml:space="preserve">sklepik </t>
+  </si>
+  <si>
+    <t>kuba</t>
+  </si>
+  <si>
+    <t>system zakupu</t>
+  </si>
+  <si>
+    <t>system pieniedzy</t>
   </si>
 </sst>
 </file>
@@ -282,12 +291,11 @@
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="9"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="4"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="5"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="8" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="5" applyFont="1"/>
@@ -647,38 +655,39 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="57.375" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="4" max="4" width="9.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="11" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="13" t="s">
         <v>37</v>
       </c>
     </row>
@@ -686,27 +695,27 @@
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" s="15" t="s">
+      <c r="C3" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="14" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" s="13" t="s">
+      <c r="C4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="12" t="s">
         <v>39</v>
       </c>
     </row>
@@ -714,27 +723,27 @@
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" s="12" t="s">
+      <c r="C5" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="11" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" s="13" t="s">
+      <c r="C6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="12" t="s">
         <v>39</v>
       </c>
     </row>
@@ -742,27 +751,27 @@
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" s="15" t="s">
+      <c r="C7" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="14" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="13" t="s">
+      <c r="C8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="12" t="s">
         <v>39</v>
       </c>
     </row>
@@ -770,55 +779,55 @@
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="12" t="s">
+      <c r="C9" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="11" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="13" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="18" t="s">
         <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" s="15" t="s">
+      <c r="C11" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="14" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="14" t="s">
+      <c r="C12" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="13" t="s">
         <v>37</v>
       </c>
     </row>
@@ -829,24 +838,24 @@
       <c r="B13" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="D13" s="15" t="s">
+      <c r="C13" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="14" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="12" t="s">
         <v>39</v>
       </c>
     </row>
@@ -857,24 +866,24 @@
       <c r="B15" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" s="12" t="s">
+      <c r="C15" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" s="11" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D16" s="13" t="s">
+      <c r="C16" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" s="12" t="s">
         <v>39</v>
       </c>
     </row>
@@ -885,24 +894,24 @@
       <c r="B17" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C17" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="D17" s="15" t="s">
+      <c r="C17" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" s="14" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D18" s="14" t="s">
+      <c r="D18" s="13" t="s">
         <v>37</v>
       </c>
     </row>
@@ -913,24 +922,24 @@
       <c r="B19" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="D19" s="15" t="s">
+      <c r="C19" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" s="14" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D20" s="14" t="s">
+      <c r="C20" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D20" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -941,24 +950,24 @@
       <c r="B21" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C21" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="D21" s="15" t="s">
+      <c r="C21" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" s="14" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D22" s="14" t="s">
+      <c r="D22" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -966,77 +975,113 @@
       <c r="A23" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="18" t="s">
+      <c r="B23" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="C23" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="D23" s="15" t="s">
+      <c r="C23" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23" s="14" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C24" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D24" s="14" t="s">
+      <c r="C24" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D24" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="18" t="s">
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C25" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="D25" s="15" t="s">
+      <c r="C25" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D25" s="14" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C26" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D26" s="13" t="s">
+      <c r="C26" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D26" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="B28" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B29" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B30" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="C30" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D27" s="15" t="s">
+      <c r="D30" s="14" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="6"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/backlog (1).xlsx
+++ b/backlog (1).xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="46">
   <si>
     <t>Rzeczy do zrobienia</t>
   </si>
@@ -165,6 +165,9 @@
   </si>
   <si>
     <t>system pieniedzy</t>
+  </si>
+  <si>
+    <t>ekwipunek</t>
   </si>
 </sst>
 </file>
@@ -647,7 +650,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -655,7 +658,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="57.375" customWidth="1"/>
@@ -726,8 +729,8 @@
       <c r="B5" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="10" t="s">
-        <v>32</v>
+      <c r="C5" s="15" t="s">
+        <v>33</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>39</v>
@@ -934,13 +937,13 @@
         <v>20</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>32</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1070,16 +1073,30 @@
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B30" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B31" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="C31" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D30" s="14" t="s">
+      <c r="D31" s="14" t="s">
         <v>38</v>
       </c>
     </row>
